--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_SURSEEDS - B. MURGI.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_SURSEEDS - B. MURGI.xlsx
@@ -565,13 +565,13 @@
         <v>21</v>
       </c>
       <c r="D2" t="n">
-        <v>65.6169</v>
+        <v>34.8045</v>
       </c>
       <c r="E2" t="n">
-        <v>57.8949</v>
+        <v>38.49</v>
       </c>
       <c r="F2" t="n">
-        <v>7.7223</v>
+        <v>-3.6856</v>
       </c>
       <c r="G2" t="n">
         <v>48.8193</v>
@@ -610,13 +610,13 @@
         <v>43.0145</v>
       </c>
       <c r="S2" t="n">
-        <v>38.5843</v>
+        <v>7.7715</v>
       </c>
       <c r="T2" t="n">
-        <v>19.229</v>
+        <v>-0.1758999999999998</v>
       </c>
       <c r="U2" t="n">
-        <v>19.3549</v>
+        <v>7.9475</v>
       </c>
       <c r="V2" t="n">
         <v>8.343300000000001</v>
@@ -643,13 +643,13 @@
         <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>11.2876</v>
+        <v>15.9243</v>
       </c>
       <c r="E3" t="n">
-        <v>28.0234</v>
+        <v>29.903</v>
       </c>
       <c r="F3" t="n">
-        <v>-16.7361</v>
+        <v>-13.9787</v>
       </c>
       <c r="G3" t="n">
         <v>22.5463</v>
@@ -688,13 +688,13 @@
         <v>34.8873</v>
       </c>
       <c r="S3" t="n">
-        <v>-11.1509</v>
+        <v>-6.5137</v>
       </c>
       <c r="T3" t="n">
-        <v>-10.9799</v>
+        <v>-9.100200000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1707999999999998</v>
+        <v>2.5866</v>
       </c>
       <c r="V3" t="n">
         <v>-1.0993</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. DAVID ROCHA</t>
+          <t>A. MORENO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D5" t="n">
-        <v>9.8963</v>
+        <v>7.2425</v>
       </c>
       <c r="E5" t="n">
-        <v>13.3484</v>
+        <v>26.7028</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.451699999999999</v>
+        <v>-19.4605</v>
       </c>
       <c r="G5" t="n">
-        <v>11.2018</v>
+        <v>38.4089</v>
       </c>
       <c r="H5" t="n">
-        <v>2.461</v>
+        <v>-8.3718</v>
       </c>
       <c r="I5" t="n">
-        <v>8.7409</v>
+        <v>46.7804</v>
       </c>
       <c r="J5" t="n">
-        <v>42.616</v>
+        <v>89.3201</v>
       </c>
       <c r="K5" t="n">
-        <v>25.1253</v>
+        <v>29.9486</v>
       </c>
       <c r="L5" t="n">
-        <v>17.4904</v>
+        <v>59.37130000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>-31.4136</v>
+        <v>-50.9112</v>
       </c>
       <c r="N5" t="n">
-        <v>-22.6643</v>
+        <v>-38.3205</v>
       </c>
       <c r="O5" t="n">
-        <v>-8.749700000000001</v>
+        <v>-12.5906</v>
       </c>
       <c r="P5" t="n">
-        <v>-13.6774</v>
+        <v>-29.1389</v>
       </c>
       <c r="Q5" t="n">
-        <v>-53.7186</v>
+        <v>-77.70350000000001</v>
       </c>
       <c r="R5" t="n">
-        <v>40.0411</v>
+        <v>48.5647</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.8789</v>
+        <v>-17.5811</v>
       </c>
       <c r="T5" t="n">
-        <v>-8.362400000000001</v>
+        <v>-12.1286</v>
       </c>
       <c r="U5" t="n">
-        <v>6.4834</v>
+        <v>-5.452199999999999</v>
       </c>
       <c r="V5" t="n">
-        <v>14.2508</v>
+        <v>15.5535</v>
       </c>
       <c r="W5" t="n">
-        <v>32.8134</v>
+        <v>27.2152</v>
       </c>
       <c r="X5" t="n">
-        <v>-18.5625</v>
+        <v>-11.6619</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T. PERERIRA</t>
+          <t>D. DAVID ROCHA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1203000000000003</v>
+        <v>6.638199999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>-5.0637</v>
+        <v>13.2196</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1841</v>
+        <v>-6.581599999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>3.4706</v>
+        <v>11.2018</v>
       </c>
       <c r="H6" t="n">
-        <v>4.1492</v>
+        <v>2.461</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6784999999999998</v>
+        <v>8.7409</v>
       </c>
       <c r="J6" t="n">
-        <v>7.2321</v>
+        <v>42.616</v>
       </c>
       <c r="K6" t="n">
-        <v>5.6652</v>
+        <v>25.1253</v>
       </c>
       <c r="L6" t="n">
-        <v>1.567</v>
+        <v>17.4904</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.7615</v>
+        <v>-31.4136</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.5161</v>
+        <v>-22.6643</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.2455</v>
+        <v>-8.749700000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.1894</v>
+        <v>-13.6774</v>
       </c>
       <c r="Q6" t="n">
-        <v>-11.2986</v>
+        <v>-53.7186</v>
       </c>
       <c r="R6" t="n">
-        <v>10.1093</v>
+        <v>40.0411</v>
       </c>
       <c r="S6" t="n">
-        <v>-2.5201</v>
+        <v>-5.1372</v>
       </c>
       <c r="T6" t="n">
-        <v>-2.7927</v>
+        <v>-8.491</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2726</v>
+        <v>3.3533</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3592</v>
+        <v>14.2508</v>
       </c>
       <c r="W6" t="n">
-        <v>1.7957</v>
+        <v>32.8134</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.4364</v>
+        <v>-18.5625</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. CABRERA PEREZ</t>
+          <t>T. PERERIRA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0891</v>
+        <v>1.8188</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0624</v>
+        <v>-4.2029</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1515</v>
+        <v>6.021699999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.3319</v>
+        <v>3.4706</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2018</v>
+        <v>4.1492</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1301</v>
+        <v>-0.6784999999999998</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>7.2321</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>5.6652</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.567</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3319</v>
+        <v>-3.7615</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2018</v>
+        <v>-1.5161</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1301</v>
+        <v>-2.2455</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1982</v>
+        <v>-1.1894</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-11.2986</v>
       </c>
       <c r="R7" t="n">
-        <v>0.1982</v>
+        <v>10.1093</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4512</v>
+        <v>-0.8216000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0624</v>
+        <v>-1.932</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3888</v>
+        <v>1.1103</v>
       </c>
       <c r="V7" t="n">
-        <v>0.674</v>
+        <v>0.3592</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.7957</v>
       </c>
       <c r="X7" t="n">
-        <v>0.674</v>
+        <v>-1.4364</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. VILLEGAS GIMENEZ</t>
+          <t>A. CABRERA PEREZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.7954</v>
+        <v>0.1172</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5807</v>
+        <v>-0.0624</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.2146</v>
+        <v>0.1796</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.4433</v>
+        <v>-0.3319</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1939</v>
+        <v>-0.2018</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.2493</v>
+        <v>-0.1301</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2085</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8072</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5988</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.6517</v>
+        <v>-0.3319</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.0012</v>
+        <v>-0.2018</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6506000000000001</v>
+        <v>-0.1301</v>
       </c>
       <c r="P8" t="n">
-        <v>1.5857</v>
+        <v>0.1982</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5857</v>
+        <v>0.1982</v>
       </c>
       <c r="S8" t="n">
-        <v>-2.1272</v>
+        <v>-0.4231</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7890999999999999</v>
+        <v>-0.0624</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.3381</v>
+        <v>-0.3607</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.8107</v>
+        <v>0.674</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.8107</v>
+        <v>0.674</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. MORENO</t>
+          <t>C. RAMON PEREZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.064599999999999</v>
+        <v>-2.1006</v>
       </c>
       <c r="E9" t="n">
-        <v>21.9023</v>
+        <v>13.6562</v>
       </c>
       <c r="F9" t="n">
-        <v>-25.9669</v>
+        <v>-15.7569</v>
       </c>
       <c r="G9" t="n">
-        <v>38.4089</v>
+        <v>0.369200000000002</v>
       </c>
       <c r="H9" t="n">
-        <v>-8.3718</v>
+        <v>-2.901099999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>46.7804</v>
+        <v>3.270199999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>89.3201</v>
+        <v>30.1623</v>
       </c>
       <c r="K9" t="n">
-        <v>29.9486</v>
+        <v>17.3779</v>
       </c>
       <c r="L9" t="n">
-        <v>59.37130000000001</v>
+        <v>12.7844</v>
       </c>
       <c r="M9" t="n">
-        <v>-50.9112</v>
+        <v>-29.7933</v>
       </c>
       <c r="N9" t="n">
-        <v>-38.3205</v>
+        <v>-20.2788</v>
       </c>
       <c r="O9" t="n">
-        <v>-12.5906</v>
+        <v>-9.514099999999999</v>
       </c>
       <c r="P9" t="n">
-        <v>-29.1389</v>
+        <v>8.126899999999999</v>
       </c>
       <c r="Q9" t="n">
-        <v>-77.70350000000001</v>
+        <v>-24.7776</v>
       </c>
       <c r="R9" t="n">
-        <v>48.5647</v>
+        <v>32.9052</v>
       </c>
       <c r="S9" t="n">
-        <v>-28.8883</v>
+        <v>-11.8856</v>
       </c>
       <c r="T9" t="n">
-        <v>-16.9292</v>
+        <v>-7.9942</v>
       </c>
       <c r="U9" t="n">
-        <v>-11.9589</v>
+        <v>-3.8915</v>
       </c>
       <c r="V9" t="n">
-        <v>15.5535</v>
+        <v>1.2887</v>
       </c>
       <c r="W9" t="n">
-        <v>27.2152</v>
+        <v>16.266</v>
       </c>
       <c r="X9" t="n">
-        <v>-11.6619</v>
+        <v>-14.9774</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. VILLEGAS ACIEN</t>
+          <t>D. VILLEGAS GIMENEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.9176</v>
+        <v>-2.9758</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.77</v>
+        <v>-0.1733</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.1477</v>
+        <v>-2.8026</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.1941</v>
+        <v>-1.4433</v>
       </c>
       <c r="H10" t="n">
-        <v>-3.064</v>
+        <v>-0.1939</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1300000000000001</v>
+        <v>-1.2493</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.6762</v>
+        <v>0.2085</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.9971</v>
+        <v>0.8072</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6791</v>
+        <v>-0.5988</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.5179999999999999</v>
+        <v>-1.6517</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.0671</v>
+        <v>-1.0012</v>
       </c>
       <c r="O10" t="n">
-        <v>0.5490999999999999</v>
+        <v>-0.6506000000000001</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.9911</v>
+        <v>1.5857</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.5857</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7323999999999999</v>
+        <v>-1.3077</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1027</v>
+        <v>-0.3817</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6296999999999999</v>
+        <v>-0.9260999999999999</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-1.8107</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.8107</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>F. PEREGRINA FEDOTOV</t>
+          <t>A. VILLEGAS ACIEN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,43 +1264,43 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.8246</v>
+        <v>-4.8543</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.2327</v>
+        <v>-3.5663</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.5919</v>
+        <v>-1.288</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.3611</v>
+        <v>-3.1941</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.6895</v>
+        <v>-3.064</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6717</v>
+        <v>-0.1300000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.498</v>
+        <v>-2.6762</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6185</v>
+        <v>-1.9971</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1205</v>
+        <v>-0.6791</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.8632</v>
+        <v>-0.5179999999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.071</v>
+        <v>-1.0671</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.7922</v>
+        <v>0.5490999999999999</v>
       </c>
       <c r="P11" t="n">
         <v>-0.9911</v>
@@ -1312,22 +1312,22 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5912999999999999</v>
+        <v>-0.6691</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.06969999999999998</v>
+        <v>0.101</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5217000000000001</v>
+        <v>-0.77</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.8811</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.674</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.0101</v>
+        <v>-5.077900000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.0366</v>
+        <v>-1.4648</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.9735</v>
+        <v>-3.6131</v>
       </c>
       <c r="G12" t="n">
         <v>-3.8092</v>
@@ -1390,13 +1390,13 @@
         <v>1.1893</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.8839</v>
+        <v>-0.9516</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.1856</v>
+        <v>-0.6137</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6983</v>
+        <v>-0.3378</v>
       </c>
       <c r="V12" t="n">
         <v>0.674</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S. MAILLO CABRERIZO</t>
+          <t>F. PEREGRINA FEDOTOV</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.5406</v>
+        <v>-5.9206</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.0364</v>
+        <v>-2.4365</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.5042</v>
+        <v>-3.4841</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.5458999999999999</v>
+        <v>-2.3611</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.1138</v>
+        <v>-1.6895</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5679999999999999</v>
+        <v>-0.6717</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4035</v>
+        <v>-0.498</v>
       </c>
       <c r="K13" t="n">
-        <v>0.283</v>
+        <v>-0.6185</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1206</v>
+        <v>0.1205</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.9492</v>
+        <v>-1.8632</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.3968</v>
+        <v>-1.071</v>
       </c>
       <c r="O13" t="n">
-        <v>0.4474</v>
+        <v>-0.7922</v>
       </c>
       <c r="P13" t="n">
-        <v>-3.3698</v>
+        <v>-0.9911</v>
       </c>
       <c r="Q13" t="n">
-        <v>-4.9555</v>
+        <v>-0.9911</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5857</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6181000000000001</v>
+        <v>-0.6872</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3085</v>
+        <v>-0.2734</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.9267</v>
+        <v>-0.414</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.0069</v>
+        <v>-1.8811</v>
       </c>
       <c r="W13" t="n">
-        <v>1.2071</v>
+        <v>-0.674</v>
       </c>
       <c r="X13" t="n">
-        <v>-3.214</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Z. AIT AISSA MOUREDI</t>
+          <t>C. VARGAS VIVANCO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D14" t="n">
-        <v>-8.192600000000001</v>
+        <v>-6.1685</v>
       </c>
       <c r="E14" t="n">
-        <v>-5.6031</v>
+        <v>1.107000000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.5896</v>
+        <v>-7.2755</v>
       </c>
       <c r="G14" t="n">
-        <v>-4.2752</v>
+        <v>4.9339</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.3519</v>
+        <v>3.466</v>
       </c>
       <c r="I14" t="n">
-        <v>-2.9234</v>
+        <v>1.468000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.8811</v>
+        <v>14.6024</v>
       </c>
       <c r="K14" t="n">
-        <v>0.3164</v>
+        <v>12.7736</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.1975</v>
+        <v>1.828900000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.3941</v>
+        <v>-9.6684</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.6684</v>
+        <v>-9.307700000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.7258</v>
+        <v>-0.3610000000000002</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.5858</v>
+        <v>-4.361000000000001</v>
       </c>
       <c r="Q14" t="n">
-        <v>-3.9644</v>
+        <v>-13.0825</v>
       </c>
       <c r="R14" t="n">
-        <v>2.3787</v>
+        <v>8.7218</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2543</v>
+        <v>-4.2014</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2534</v>
+        <v>-4.3004</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5077</v>
+        <v>0.09920000000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>-2.0773</v>
+        <v>-2.54</v>
       </c>
       <c r="W14" t="n">
-        <v>-1.011</v>
+        <v>3.8879</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.0664</v>
+        <v>-6.4279</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C. VARGAS VIVANCO</t>
+          <t>S. MAILLO CABRERIZO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>-9.2064</v>
+        <v>-6.6777</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.138300000000001</v>
+        <v>-3.342000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>-9.0679</v>
+        <v>-3.3358</v>
       </c>
       <c r="G15" t="n">
-        <v>4.9339</v>
+        <v>-0.5458999999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>3.466</v>
+        <v>-1.1138</v>
       </c>
       <c r="I15" t="n">
-        <v>1.468000000000001</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>14.6024</v>
+        <v>0.4035</v>
       </c>
       <c r="K15" t="n">
-        <v>12.7736</v>
+        <v>0.283</v>
       </c>
       <c r="L15" t="n">
-        <v>1.828900000000001</v>
+        <v>0.1206</v>
       </c>
       <c r="M15" t="n">
-        <v>-9.6684</v>
+        <v>-0.9492</v>
       </c>
       <c r="N15" t="n">
-        <v>-9.307700000000001</v>
+        <v>-1.3968</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.3610000000000002</v>
+        <v>0.4474</v>
       </c>
       <c r="P15" t="n">
-        <v>-4.361000000000001</v>
+        <v>-3.3698</v>
       </c>
       <c r="Q15" t="n">
-        <v>-13.0825</v>
+        <v>-4.9555</v>
       </c>
       <c r="R15" t="n">
-        <v>8.7218</v>
+        <v>1.5857</v>
       </c>
       <c r="S15" t="n">
-        <v>-7.2393</v>
+        <v>-0.7553000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>-5.5458</v>
+        <v>0.002900000000000003</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.6934</v>
+        <v>-0.7582</v>
       </c>
       <c r="V15" t="n">
-        <v>-2.54</v>
+        <v>-2.0069</v>
       </c>
       <c r="W15" t="n">
-        <v>3.8879</v>
+        <v>1.2071</v>
       </c>
       <c r="X15" t="n">
-        <v>-6.4279</v>
+        <v>-3.214</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C. RAMON PEREZ</t>
+          <t>Z. AIT AISSA MOUREDI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,70 +1654,70 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>-12.9431</v>
+        <v>-8.098000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>9.348199999999999</v>
+        <v>-5.705</v>
       </c>
       <c r="F16" t="n">
-        <v>-22.2915</v>
+        <v>-2.393</v>
       </c>
       <c r="G16" t="n">
-        <v>0.369200000000002</v>
+        <v>-4.2752</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.901099999999999</v>
+        <v>-1.3519</v>
       </c>
       <c r="I16" t="n">
-        <v>3.270199999999999</v>
+        <v>-2.9234</v>
       </c>
       <c r="J16" t="n">
-        <v>30.1623</v>
+        <v>-0.8811</v>
       </c>
       <c r="K16" t="n">
-        <v>17.3779</v>
+        <v>0.3164</v>
       </c>
       <c r="L16" t="n">
-        <v>12.7844</v>
+        <v>-1.1975</v>
       </c>
       <c r="M16" t="n">
-        <v>-29.7933</v>
+        <v>-3.3941</v>
       </c>
       <c r="N16" t="n">
-        <v>-20.2788</v>
+        <v>-1.6684</v>
       </c>
       <c r="O16" t="n">
-        <v>-9.514099999999999</v>
+        <v>-1.7258</v>
       </c>
       <c r="P16" t="n">
-        <v>8.126899999999999</v>
+        <v>-1.5858</v>
       </c>
       <c r="Q16" t="n">
-        <v>-24.7776</v>
+        <v>-3.9644</v>
       </c>
       <c r="R16" t="n">
-        <v>32.9052</v>
+        <v>2.3787</v>
       </c>
       <c r="S16" t="n">
-        <v>-22.7281</v>
+        <v>-0.1597</v>
       </c>
       <c r="T16" t="n">
-        <v>-12.302</v>
+        <v>0.1515</v>
       </c>
       <c r="U16" t="n">
-        <v>-10.4259</v>
+        <v>-0.3111</v>
       </c>
       <c r="V16" t="n">
-        <v>1.2887</v>
+        <v>-2.0773</v>
       </c>
       <c r="W16" t="n">
-        <v>16.266</v>
+        <v>-1.011</v>
       </c>
       <c r="X16" t="n">
-        <v>-14.9774</v>
+        <v>-1.0664</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>24</v>
       </c>
       <c r="D17" t="n">
-        <v>-14.1778</v>
+        <v>-8.531099999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.4045</v>
+        <v>0.3334000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>-12.7733</v>
+        <v>-8.864500000000001</v>
       </c>
       <c r="G17" t="n">
         <v>-19.2306</v>
@@ -1780,13 +1780,13 @@
         <v>37.6623</v>
       </c>
       <c r="S17" t="n">
-        <v>-11.4032</v>
+        <v>-5.7561</v>
       </c>
       <c r="T17" t="n">
-        <v>-11.2661</v>
+        <v>-9.527799999999999</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1371000000000003</v>
+        <v>3.7715</v>
       </c>
       <c r="V17" t="n">
         <v>-3.9613</v>
@@ -1813,13 +1813,13 @@
         <v>11</v>
       </c>
       <c r="D18" t="n">
-        <v>-15.8758</v>
+        <v>-13.0326</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.6712</v>
+        <v>-2.1432</v>
       </c>
       <c r="F18" t="n">
-        <v>-12.2045</v>
+        <v>-10.8894</v>
       </c>
       <c r="G18" t="n">
         <v>-5.0475</v>
@@ -1858,13 +1858,13 @@
         <v>2.9732</v>
       </c>
       <c r="S18" t="n">
-        <v>-3.4756</v>
+        <v>-0.6323</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.7434</v>
+        <v>-0.2152999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.7322</v>
+        <v>-0.417</v>
       </c>
       <c r="V18" t="n">
         <v>-5.9652</v>
@@ -1891,13 +1891,13 @@
         <v>24</v>
       </c>
       <c r="D19" t="n">
-        <v>-19.5385</v>
+        <v>-20.5777</v>
       </c>
       <c r="E19" t="n">
-        <v>-16.3012</v>
+        <v>-16.0912</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.2376</v>
+        <v>-4.4867</v>
       </c>
       <c r="G19" t="n">
         <v>18.5729</v>
@@ -1936,13 +1936,13 @@
         <v>25.769</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.8394</v>
+        <v>-2.8786</v>
       </c>
       <c r="T19" t="n">
-        <v>-5.519</v>
+        <v>-5.3086</v>
       </c>
       <c r="U19" t="n">
-        <v>3.6793</v>
+        <v>2.4304</v>
       </c>
       <c r="V19" t="n">
         <v>-12.2873</v>
@@ -1969,13 +1969,13 @@
         <v>26</v>
       </c>
       <c r="D20" t="n">
-        <v>-30.8295</v>
+        <v>-21.9892</v>
       </c>
       <c r="E20" t="n">
-        <v>-10.4407</v>
+        <v>-4.1288</v>
       </c>
       <c r="F20" t="n">
-        <v>-20.3888</v>
+        <v>-17.8603</v>
       </c>
       <c r="G20" t="n">
         <v>4.634499999999999</v>
@@ -2014,13 +2014,13 @@
         <v>40.2392</v>
       </c>
       <c r="S20" t="n">
-        <v>-19.65</v>
+        <v>-10.8095</v>
       </c>
       <c r="T20" t="n">
-        <v>-19.1211</v>
+        <v>-12.8089</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5288999999999997</v>
+        <v>1.9995</v>
       </c>
       <c r="V20" t="n">
         <v>-19.9765</v>
@@ -2047,13 +2047,13 @@
         <v>23</v>
       </c>
       <c r="D21" t="n">
-        <v>-32.3748</v>
+        <v>-28.8823</v>
       </c>
       <c r="E21" t="n">
-        <v>-16.0519</v>
+        <v>-15.293</v>
       </c>
       <c r="F21" t="n">
-        <v>-16.3227</v>
+        <v>-13.5889</v>
       </c>
       <c r="G21" t="n">
         <v>-19.7205</v>
@@ -2092,13 +2092,13 @@
         <v>12.0915</v>
       </c>
       <c r="S21" t="n">
-        <v>-6.7987</v>
+        <v>-3.3056</v>
       </c>
       <c r="T21" t="n">
-        <v>-3.4718</v>
+        <v>-2.7126</v>
       </c>
       <c r="U21" t="n">
-        <v>-3.3272</v>
+        <v>-0.593</v>
       </c>
       <c r="V21" t="n">
         <v>-5.8555</v>
@@ -2125,13 +2125,13 @@
         <v>26</v>
       </c>
       <c r="D22" t="n">
-        <v>-77.32769999999999</v>
+        <v>-58.3873</v>
       </c>
       <c r="E22" t="n">
-        <v>70.07729999999999</v>
+        <v>74.7561</v>
       </c>
       <c r="F22" t="n">
-        <v>-147.4046</v>
+        <v>-133.1439</v>
       </c>
       <c r="G22" t="n">
         <v>102.9516</v>
@@ -2143,7 +2143,7 @@
         <v>79.74360000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>430.6051</v>
+        <v>430.6050999999999</v>
       </c>
       <c r="K22" t="n">
         <v>253.5451</v>
@@ -2158,10 +2158,10 @@
         <v>-230.3369</v>
       </c>
       <c r="O22" t="n">
-        <v>-97.3165</v>
+        <v>-97.31649999999999</v>
       </c>
       <c r="P22" t="n">
-        <v>-76.3173</v>
+        <v>-76.31730000000002</v>
       </c>
       <c r="Q22" t="n">
         <v>-420.2306000000001</v>
@@ -2170,13 +2170,13 @@
         <v>343.9167</v>
       </c>
       <c r="S22" t="n">
-        <v>-85.64659999999999</v>
+        <v>-66.70490000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>-80.452</v>
+        <v>-75.77129999999998</v>
       </c>
       <c r="U22" t="n">
-        <v>-5.195199999999997</v>
+        <v>9.066700000000001</v>
       </c>
       <c r="V22" t="n">
         <v>-18.3176</v>
